--- a/data_plan_capstone.xlsx
+++ b/data_plan_capstone.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabri\Documents\research_capstone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CEB436F-4FEE-4272-82D0-48B066100647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD436954-E22E-4A33-8516-FABDBC1091AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{84021EAC-F933-478D-95E5-945724B0C9EB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{84021EAC-F933-478D-95E5-945724B0C9EB}"/>
   </bookViews>
   <sheets>
     <sheet name="ut_bills" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="215">
   <si>
     <t>bill_id</t>
   </si>
@@ -291,9 +291,6 @@
   </si>
   <si>
     <t>location_stage</t>
-  </si>
-  <si>
-    <t>subject_group</t>
   </si>
   <si>
     <t>characters(Education, Healthcare…)</t>
@@ -661,6 +658,39 @@
   </si>
   <si>
     <t>Inflation adjusted total amount of money appropriated in the bill</t>
+  </si>
+  <si>
+    <t>stage_0</t>
+  </si>
+  <si>
+    <t>stage_1</t>
+  </si>
+  <si>
+    <t>stage_2</t>
+  </si>
+  <si>
+    <t>stage_3</t>
+  </si>
+  <si>
+    <t>subject_groups</t>
+  </si>
+  <si>
+    <t>no_subject</t>
+  </si>
+  <si>
+    <t>Binary-coded variable, if bill didn't leave it's original chamber</t>
+  </si>
+  <si>
+    <t>Binary-coded variable, if bill went to another chamber</t>
+  </si>
+  <si>
+    <t>No subject</t>
+  </si>
+  <si>
+    <t>Binary-coded variable, if bill went outside of the chamber but did not get signed into law</t>
+  </si>
+  <si>
+    <t>Signed into law</t>
   </si>
 </sst>
 </file>
@@ -708,48 +738,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1100,7 +1099,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07347EA0-385C-4B0A-8BAB-822EDDEC5A8B}">
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
@@ -1131,10 +1130,10 @@
         <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>23</v>
@@ -1227,7 +1226,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1238,7 +1237,7 @@
         <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E7">
         <v>2023</v>
@@ -1253,7 +1252,7 @@
         <v>30</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -1267,7 +1266,7 @@
         <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>57</v>
@@ -1279,7 +1278,7 @@
         <v>30</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>71</v>
@@ -1362,22 +1361,22 @@
         <v>58</v>
       </c>
       <c r="E12" t="s">
+        <v>148</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G12" t="s">
+        <v>128</v>
+      </c>
+      <c r="H12" t="s">
         <v>149</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="G12" t="s">
-        <v>129</v>
-      </c>
-      <c r="H12" t="s">
-        <v>150</v>
-      </c>
-      <c r="I12" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -1391,7 +1390,7 @@
         <v>80</v>
       </c>
       <c r="D13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E13">
         <v>2023</v>
@@ -1406,7 +1405,7 @@
         <v>82</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -1426,7 +1425,7 @@
         <v>30</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -1449,11 +1448,11 @@
         <v>53</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" t="s">
         <v>12</v>
       </c>
       <c r="B16" t="s">
@@ -1463,7 +1462,7 @@
         <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>66</v>
@@ -1475,10 +1474,10 @@
         <v>30</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
@@ -1492,7 +1491,7 @@
         <v>67</v>
       </c>
       <c r="D17" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>68</v>
@@ -1501,7 +1500,7 @@
         <v>30</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -1532,7 +1531,7 @@
         <v>74</v>
       </c>
       <c r="D19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>75</v>
@@ -1541,7 +1540,7 @@
         <v>30</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -1592,7 +1591,7 @@
         <v>79</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G22" t="s">
         <v>44</v>
@@ -1601,18 +1600,18 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="B23" t="s">
         <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G23" t="s">
         <v>41</v>
@@ -1621,18 +1620,18 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>84</v>
+        <v>204</v>
       </c>
       <c r="B24" t="s">
         <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>36</v>
+        <v>210</v>
       </c>
       <c r="G24" t="s">
         <v>41</v>
@@ -1643,30 +1642,27 @@
     </row>
     <row r="25" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>85</v>
+        <v>205</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>131</v>
+        <v>211</v>
       </c>
       <c r="G25" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="H25" t="s">
         <v>31</v>
       </c>
-      <c r="I25" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>87</v>
+        <v>206</v>
       </c>
       <c r="B26" t="s">
         <v>26</v>
@@ -1675,10 +1671,10 @@
         <v>33</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>107</v>
+        <v>213</v>
       </c>
       <c r="G26" t="s">
-        <v>129</v>
+        <v>41</v>
       </c>
       <c r="H26" t="s">
         <v>31</v>
@@ -1686,7 +1682,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>88</v>
+        <v>207</v>
       </c>
       <c r="B27" t="s">
         <v>26</v>
@@ -1695,58 +1691,61 @@
         <v>33</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>108</v>
+        <v>214</v>
       </c>
       <c r="G27" t="s">
+        <v>41</v>
+      </c>
+      <c r="H27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" t="s">
+        <v>33</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G28" t="s">
+        <v>41</v>
+      </c>
+      <c r="H28" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>208</v>
+      </c>
+      <c r="B29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" t="s">
+        <v>85</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G29" t="s">
+        <v>83</v>
+      </c>
+      <c r="H29" t="s">
+        <v>31</v>
+      </c>
+      <c r="I29" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="H27" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>89</v>
-      </c>
-      <c r="B28" t="s">
-        <v>26</v>
-      </c>
-      <c r="C28" t="s">
-        <v>33</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="G28" t="s">
-        <v>129</v>
-      </c>
-      <c r="H28" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>90</v>
-      </c>
-      <c r="B29" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29" t="s">
-        <v>33</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G29" t="s">
-        <v>129</v>
-      </c>
-      <c r="H29" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B30" t="s">
         <v>26</v>
@@ -1755,10 +1754,10 @@
         <v>33</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="G30" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H30" t="s">
         <v>31</v>
@@ -1766,7 +1765,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B31" t="s">
         <v>26</v>
@@ -1775,10 +1774,10 @@
         <v>33</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H31" t="s">
         <v>31</v>
@@ -1786,7 +1785,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>127</v>
+        <v>88</v>
       </c>
       <c r="B32" t="s">
         <v>26</v>
@@ -1795,10 +1794,10 @@
         <v>33</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="G32" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H32" t="s">
         <v>31</v>
@@ -1806,7 +1805,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B33" t="s">
         <v>26</v>
@@ -1815,10 +1814,10 @@
         <v>33</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G33" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H33" t="s">
         <v>31</v>
@@ -1826,7 +1825,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B34" t="s">
         <v>26</v>
@@ -1835,10 +1834,10 @@
         <v>33</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H34" t="s">
         <v>31</v>
@@ -1846,7 +1845,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B35" t="s">
         <v>26</v>
@@ -1855,10 +1854,10 @@
         <v>33</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G35" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H35" t="s">
         <v>31</v>
@@ -1866,7 +1865,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="B36" t="s">
         <v>26</v>
@@ -1875,10 +1874,10 @@
         <v>33</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="G36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H36" t="s">
         <v>31</v>
@@ -1886,7 +1885,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B37" t="s">
         <v>26</v>
@@ -1895,10 +1894,10 @@
         <v>33</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="G37" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H37" t="s">
         <v>31</v>
@@ -1906,7 +1905,7 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B38" t="s">
         <v>26</v>
@@ -1915,10 +1914,10 @@
         <v>33</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G38" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H38" t="s">
         <v>31</v>
@@ -1926,7 +1925,7 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B39" t="s">
         <v>26</v>
@@ -1935,10 +1934,10 @@
         <v>33</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G39" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H39" t="s">
         <v>31</v>
@@ -1946,7 +1945,7 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B40" t="s">
         <v>26</v>
@@ -1955,10 +1954,10 @@
         <v>33</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G40" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H40" t="s">
         <v>31</v>
@@ -1966,7 +1965,7 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B41" t="s">
         <v>26</v>
@@ -1975,10 +1974,10 @@
         <v>33</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G41" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H41" t="s">
         <v>31</v>
@@ -1986,7 +1985,7 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B42" t="s">
         <v>26</v>
@@ -1995,10 +1994,10 @@
         <v>33</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G42" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H42" t="s">
         <v>31</v>
@@ -2006,7 +2005,7 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B43" t="s">
         <v>26</v>
@@ -2015,10 +2014,10 @@
         <v>33</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="G43" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H43" t="s">
         <v>31</v>
@@ -2026,7 +2025,7 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B44" t="s">
         <v>26</v>
@@ -2035,10 +2034,10 @@
         <v>33</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="G44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H44" t="s">
         <v>31</v>
@@ -2046,7 +2045,7 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B45" t="s">
         <v>26</v>
@@ -2055,10 +2054,10 @@
         <v>33</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G45" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H45" t="s">
         <v>31</v>
@@ -2066,7 +2065,7 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>106</v>
+        <v>209</v>
       </c>
       <c r="B46" t="s">
         <v>26</v>
@@ -2075,10 +2074,10 @@
         <v>33</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="G46" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H46" t="s">
         <v>31</v>
@@ -2086,7 +2085,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>151</v>
+        <v>101</v>
       </c>
       <c r="B47" t="s">
         <v>26</v>
@@ -2095,10 +2094,10 @@
         <v>33</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="G47" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H47" t="s">
         <v>31</v>
@@ -2106,7 +2105,7 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>153</v>
+        <v>102</v>
       </c>
       <c r="B48" t="s">
         <v>26</v>
@@ -2114,14 +2113,11 @@
       <c r="C48" t="s">
         <v>33</v>
       </c>
-      <c r="E48">
-        <v>2023</v>
-      </c>
       <c r="F48" s="1" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="G48" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H48" t="s">
         <v>31</v>
@@ -2129,7 +2125,7 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="B49" t="s">
         <v>26</v>
@@ -2138,10 +2134,10 @@
         <v>33</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="G49" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H49" t="s">
         <v>31</v>
@@ -2149,7 +2145,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>163</v>
+        <v>104</v>
       </c>
       <c r="B50" t="s">
         <v>26</v>
@@ -2158,10 +2154,10 @@
         <v>33</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="G50" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H50" t="s">
         <v>31</v>
@@ -2169,171 +2165,174 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>105</v>
+      </c>
+      <c r="B51" t="s">
+        <v>26</v>
+      </c>
+      <c r="C51" t="s">
+        <v>33</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G51" t="s">
+        <v>128</v>
+      </c>
+      <c r="H51" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>150</v>
+      </c>
+      <c r="B52" t="s">
+        <v>26</v>
+      </c>
+      <c r="C52" t="s">
+        <v>33</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G52" t="s">
+        <v>128</v>
+      </c>
+      <c r="H52" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>152</v>
+      </c>
+      <c r="B53" t="s">
+        <v>26</v>
+      </c>
+      <c r="C53" t="s">
+        <v>33</v>
+      </c>
+      <c r="E53">
+        <v>2023</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G53" t="s">
+        <v>128</v>
+      </c>
+      <c r="H53" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>154</v>
+      </c>
+      <c r="B54" t="s">
+        <v>26</v>
+      </c>
+      <c r="C54" t="s">
+        <v>33</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G54" t="s">
+        <v>128</v>
+      </c>
+      <c r="H54" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>162</v>
+      </c>
+      <c r="B55" t="s">
+        <v>26</v>
+      </c>
+      <c r="C55" t="s">
+        <v>33</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G55" t="s">
+        <v>128</v>
+      </c>
+      <c r="H55" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>156</v>
+      </c>
+      <c r="B56" t="s">
+        <v>26</v>
+      </c>
+      <c r="C56" t="s">
+        <v>165</v>
+      </c>
+      <c r="E56">
+        <v>2023</v>
+      </c>
+      <c r="F56" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B51" t="s">
-        <v>26</v>
-      </c>
-      <c r="C51" t="s">
-        <v>166</v>
-      </c>
-      <c r="E51">
-        <v>2023</v>
-      </c>
-      <c r="F51" s="1" t="s">
+      <c r="G56" t="s">
+        <v>128</v>
+      </c>
+      <c r="H56" t="s">
+        <v>31</v>
+      </c>
+      <c r="J56" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="G51" t="s">
-        <v>129</v>
-      </c>
-      <c r="H51" t="s">
-        <v>31</v>
-      </c>
-      <c r="J51" s="1" t="s">
+    </row>
+    <row r="57" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="B57" t="s">
+        <v>26</v>
+      </c>
+      <c r="C57" t="s">
+        <v>58</v>
+      </c>
+      <c r="E57">
+        <v>2016</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B52" t="s">
-        <v>26</v>
-      </c>
-      <c r="C52" t="s">
-        <v>58</v>
-      </c>
-      <c r="E52">
-        <v>2016</v>
-      </c>
-      <c r="F52" s="1" t="s">
+      <c r="G57" t="s">
+        <v>128</v>
+      </c>
+      <c r="H57" t="s">
+        <v>31</v>
+      </c>
+      <c r="J57" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="G52" t="s">
-        <v>129</v>
-      </c>
-      <c r="H52" t="s">
-        <v>31</v>
-      </c>
-      <c r="J52" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>173</v>
-      </c>
-      <c r="B53" t="s">
-        <v>182</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="E53" t="s">
-        <v>183</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H53" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>174</v>
-      </c>
-      <c r="B54" t="s">
-        <v>182</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="E54" t="s">
-        <v>183</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="H54" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>175</v>
-      </c>
-      <c r="B55" t="s">
-        <v>182</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E55" t="s">
-        <v>183</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="H55" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>176</v>
-      </c>
-      <c r="B56" t="s">
-        <v>182</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E56" t="s">
-        <v>183</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="H56" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>177</v>
-      </c>
-      <c r="B57" t="s">
-        <v>182</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="E57" t="s">
-        <v>183</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="H57" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B58" t="s">
+        <v>181</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E58" t="s">
         <v>182</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="E58" t="s">
+      <c r="F58" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>195</v>
       </c>
       <c r="H58" t="s">
         <v>30</v>
@@ -2341,117 +2340,215 @@
     </row>
     <row r="59" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B59" t="s">
+        <v>181</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E59" t="s">
         <v>182</v>
       </c>
-      <c r="C59" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E59" t="s">
-        <v>196</v>
-      </c>
       <c r="F59" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="G59" t="s">
-        <v>83</v>
+        <v>186</v>
       </c>
       <c r="H59" t="s">
         <v>30</v>
       </c>
-      <c r="I59" s="1" t="s">
-        <v>198</v>
-      </c>
     </row>
     <row r="60" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B60" t="s">
+        <v>181</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E60" t="s">
         <v>182</v>
       </c>
-      <c r="C60" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="E60" t="s">
-        <v>196</v>
-      </c>
       <c r="F60" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="G60" t="s">
-        <v>129</v>
+        <v>188</v>
       </c>
       <c r="H60" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="B61" t="s">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="E61" t="s">
-        <v>77</v>
+        <v>182</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="G61" t="s">
-        <v>83</v>
+        <v>190</v>
       </c>
       <c r="H61" t="s">
-        <v>31</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>168</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>176</v>
+      </c>
+      <c r="B62" t="s">
         <v>181</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E62" t="s">
         <v>182</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="F62" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="H62" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>177</v>
+      </c>
+      <c r="B63" t="s">
+        <v>181</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E63" t="s">
+        <v>182</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H63" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>178</v>
+      </c>
+      <c r="B64" t="s">
+        <v>181</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E64" t="s">
+        <v>195</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G64" t="s">
+        <v>83</v>
+      </c>
+      <c r="H64" t="s">
+        <v>30</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>179</v>
+      </c>
+      <c r="B65" t="s">
+        <v>181</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E65" t="s">
+        <v>195</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G65" t="s">
+        <v>128</v>
+      </c>
+      <c r="H65" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>163</v>
+      </c>
+      <c r="B66" t="s">
+        <v>26</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E66" t="s">
+        <v>77</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G66" t="s">
+        <v>83</v>
+      </c>
+      <c r="H66" t="s">
+        <v>31</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>180</v>
+      </c>
+      <c r="B67" t="s">
+        <v>181</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E67" t="s">
+        <v>77</v>
+      </c>
+      <c r="F67" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E62" t="s">
-        <v>77</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G62" t="s">
-        <v>129</v>
-      </c>
-      <c r="H62" t="s">
+      <c r="G67" t="s">
+        <v>128</v>
+      </c>
+      <c r="H67" t="s">
         <v>31</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="G63:G1048576 G1:G61 H53:H60">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+  <conditionalFormatting sqref="H58:H65 G68:G1048576 H46 G1:G66">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"Outcome"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
-      <formula>"Covariate"</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G1:G1048576 H53:H60">
+  <conditionalFormatting sqref="H58:H65 H46 G1:G1048576">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Covariate"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data_plan_capstone.xlsx
+++ b/data_plan_capstone.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabri\Documents\research_capstone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD436954-E22E-4A33-8516-FABDBC1091AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1A31C6-49DE-46A5-9AD4-D3817D18D1C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{84021EAC-F933-478D-95E5-945724B0C9EB}"/>
   </bookViews>
   <sheets>
     <sheet name="ut_bills" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="162">
   <si>
     <t>bill_id</t>
   </si>
@@ -143,9 +144,6 @@
     <t>Binary-coded variable if bill was enacted/passed or not; 1 passed, else 0</t>
   </si>
   <si>
-    <t>0-3 (inclusive)</t>
-  </si>
-  <si>
     <t>Ordinal range of the final stage of the bill; 0 is it died in the originating house/committee, 3 is it passed</t>
   </si>
   <si>
@@ -296,141 +294,15 @@
     <t>characters(Education, Healthcare…)</t>
   </si>
   <si>
-    <t>agri_food</t>
-  </si>
-  <si>
-    <t>arts_cult_rec</t>
-  </si>
-  <si>
-    <t>bus_comm</t>
-  </si>
-  <si>
-    <t>civ_rights_libs</t>
-  </si>
-  <si>
-    <t>crim_justice</t>
-  </si>
-  <si>
-    <t>econ_dev</t>
-  </si>
-  <si>
-    <t>elect_gov</t>
-  </si>
-  <si>
-    <t>energy</t>
-  </si>
-  <si>
     <t>env_nr</t>
   </si>
   <si>
-    <t>fam_ss</t>
-  </si>
-  <si>
-    <t>health_care</t>
-  </si>
-  <si>
-    <t>higher_ed</t>
-  </si>
-  <si>
-    <t>house_land_use</t>
-  </si>
-  <si>
-    <t>labor_ee</t>
-  </si>
-  <si>
-    <t>local_gov</t>
-  </si>
-  <si>
-    <t>pub_safe_emerg</t>
-  </si>
-  <si>
-    <t>retire_ben</t>
-  </si>
-  <si>
-    <t>tax_fin</t>
-  </si>
-  <si>
-    <t>tech_data</t>
-  </si>
-  <si>
-    <t>transpo</t>
-  </si>
-  <si>
-    <t>Agriculture &amp; Food; 1 yes, 0 no</t>
-  </si>
-  <si>
-    <t>Arts, Culture, &amp; Recreation</t>
-  </si>
-  <si>
-    <t>Business &amp; Commerce</t>
-  </si>
-  <si>
-    <t>Civil Rights &amp; Liberties</t>
-  </si>
-  <si>
-    <t>Criminal Justice</t>
-  </si>
-  <si>
-    <t>Economic Development</t>
-  </si>
-  <si>
-    <t>Elections &amp; Government Ops</t>
-  </si>
-  <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t>Environment &amp; Natural Resources</t>
-  </si>
-  <si>
-    <t>Family &amp; Social Svcs</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>Higher Education</t>
-  </si>
-  <si>
-    <t>Housing &amp; Land Use</t>
-  </si>
-  <si>
-    <t>Labor &amp; Employment</t>
-  </si>
-  <si>
-    <t>Local Gov</t>
-  </si>
-  <si>
-    <t>Public Safety &amp; Emergency Svcs</t>
-  </si>
-  <si>
-    <t>Retirement &amp; Benefits</t>
-  </si>
-  <si>
-    <t>Taxes &amp; Finance</t>
-  </si>
-  <si>
-    <t>Technology &amp; Data</t>
-  </si>
-  <si>
-    <t>Transportation</t>
-  </si>
-  <si>
-    <t>ed_k12</t>
-  </si>
-  <si>
-    <t>Education (K-12)</t>
-  </si>
-  <si>
     <t>Covariate</t>
   </si>
   <si>
     <t>CLEAN: Need 'No Subject' column</t>
   </si>
   <si>
-    <t>List of subject groups the bill falls into (22 groups total)</t>
-  </si>
-  <si>
     <t>NAs</t>
   </si>
   <si>
@@ -512,36 +384,18 @@
     <t>Number of cosponsors the bill had</t>
   </si>
   <si>
-    <t>The more cosponsors, the more support there was</t>
-  </si>
-  <si>
     <t>num_sub_new</t>
   </si>
   <si>
     <t>Derived number of substitutes based on the substitute # of the active/enrolled bill</t>
   </si>
   <si>
-    <t>Not the best for regression; may measure "a substitute was passed" instead of "how many substitutes did it have". BUT applies to all years instead of 2025 and on.</t>
-  </si>
-  <si>
     <t>money1</t>
   </si>
   <si>
-    <t>money_sum</t>
-  </si>
-  <si>
     <t>If the bill had money appropriated</t>
   </si>
   <si>
-    <t>0-67</t>
-  </si>
-  <si>
-    <t>Total amount of money appropriated in the bill (in $ amounts)</t>
-  </si>
-  <si>
-    <t>CLEAN: need to adjust values for inflation</t>
-  </si>
-  <si>
     <t>Session id on website</t>
   </si>
   <si>
@@ -557,112 +411,33 @@
     <t>unemp_rate</t>
   </si>
   <si>
-    <t>unemp_rate_chg</t>
-  </si>
-  <si>
-    <t>unemp_rate_pct</t>
-  </si>
-  <si>
-    <t>real_gdp</t>
-  </si>
-  <si>
     <t>real_gdp_chg</t>
   </si>
   <si>
     <t>real_gdp_pct</t>
   </si>
   <si>
-    <t>gfund_nom</t>
-  </si>
-  <si>
     <t>gfund_real</t>
   </si>
   <si>
     <t>money_sum_real</t>
   </si>
   <si>
-    <t>float64</t>
-  </si>
-  <si>
-    <t>2016-2024</t>
-  </si>
-  <si>
     <t>Utah annual unemployment rate</t>
   </si>
   <si>
-    <t>min: -2
-max: 2.3</t>
-  </si>
-  <si>
-    <t>min:  2.4
-max: 4.8</t>
-  </si>
-  <si>
-    <t>Level change in unemp_rate</t>
-  </si>
-  <si>
-    <t>min: -41.67
-max: 92</t>
-  </si>
-  <si>
-    <t>Percent change in unemp_rate</t>
-  </si>
-  <si>
-    <t>min: 162528.2
-max: 234300.6</t>
-  </si>
-  <si>
-    <t>Utah annual real GDP (millions of chained 2017 $)</t>
-  </si>
-  <si>
-    <t>min: 2562.6
-max: 15966.3</t>
-  </si>
-  <si>
     <t>Level change in real_gdp</t>
   </si>
   <si>
-    <t>min: 1.329420
-max: 8.174300</t>
-  </si>
-  <si>
     <t>Percent change in real_gdp</t>
   </si>
   <si>
-    <t>2016-2025</t>
-  </si>
-  <si>
-    <t>Nominal amount of general fund revenues in a given year</t>
-  </si>
-  <si>
-    <t>Pulled from COBI</t>
-  </si>
-  <si>
     <t>Inflation adjusted amount of general fund revenues in a given year</t>
   </si>
   <si>
-    <t>min: $7.822419e+09
-max: $1.620825e+10</t>
-  </si>
-  <si>
-    <t>min: $1.049292e+10
-max: $1.657039e+10</t>
-  </si>
-  <si>
-    <t>min: $0
-max: $2.324460e+09</t>
-  </si>
-  <si>
-    <t>min: $0
-max: $2.557085e+09</t>
-  </si>
-  <si>
     <t>Inflation adjusted total amount of money appropriated in the bill</t>
   </si>
   <si>
-    <t>stage_0</t>
-  </si>
-  <si>
     <t>stage_1</t>
   </si>
   <si>
@@ -672,25 +447,82 @@
     <t>stage_3</t>
   </si>
   <si>
-    <t>subject_groups</t>
-  </si>
-  <si>
-    <t>no_subject</t>
-  </si>
-  <si>
     <t>Binary-coded variable, if bill didn't leave it's original chamber</t>
   </si>
   <si>
     <t>Binary-coded variable, if bill went to another chamber</t>
   </si>
   <si>
-    <t>No subject</t>
-  </si>
-  <si>
     <t>Binary-coded variable, if bill went outside of the chamber but did not get signed into law</t>
   </si>
   <si>
     <t>Signed into law</t>
+  </si>
+  <si>
+    <t>stage_4</t>
+  </si>
+  <si>
+    <t>subject_group</t>
+  </si>
+  <si>
+    <t>educ</t>
+  </si>
+  <si>
+    <t>cj_civ</t>
+  </si>
+  <si>
+    <t>econ</t>
+  </si>
+  <si>
+    <t>health</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>gov_ops</t>
+  </si>
+  <si>
+    <t>party</t>
+  </si>
+  <si>
+    <t>party1</t>
+  </si>
+  <si>
+    <t>Criminal Justice and Civics (courts, rights, liberties)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economy (business &amp; comm, tech &amp; data, econ dev, labor &amp; employement, house and land use, </t>
+  </si>
+  <si>
+    <t>Health (health, family and social svcs)</t>
+  </si>
+  <si>
+    <t>all other bills, includes no subject</t>
+  </si>
+  <si>
+    <t>Primary subject group is education (k-12, higher ed)</t>
+  </si>
+  <si>
+    <t>List of subject groups the bill falls into (7 groups total)</t>
+  </si>
+  <si>
+    <t>Government operations (tax &amp; finance, local gov, election &amp; gov)</t>
+  </si>
+  <si>
+    <t>Environment &amp; natural resources (env_nr, agri &amp; food)</t>
+  </si>
+  <si>
+    <t>Sponsor party</t>
+  </si>
+  <si>
+    <t>character</t>
+  </si>
+  <si>
+    <t>Rep, Dem, FWD</t>
+  </si>
+  <si>
+    <t>Majority party variable: 1 if Rep, 0 if other (both Dem and FWD)</t>
   </si>
 </sst>
 </file>
@@ -738,12 +570,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1099,7 +932,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07347EA0-385C-4B0A-8BAB-822EDDEC5A8B}">
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
@@ -1130,10 +963,10 @@
         <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>23</v>
@@ -1148,13 +981,13 @@
         <v>24</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L3" t="s">
+        <v>68</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -1165,19 +998,19 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="G4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="H4" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -1188,19 +1021,19 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="G5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
@@ -1211,19 +1044,19 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H6" t="s">
         <v>30</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
@@ -1234,25 +1067,25 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>132</v>
+        <v>89</v>
       </c>
       <c r="E7">
         <v>2023</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H7" t="s">
         <v>30</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>139</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -1263,25 +1096,25 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>133</v>
+        <v>90</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s">
         <v>30</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -1292,16 +1125,16 @@
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H9" t="s">
         <v>30</v>
@@ -1315,16 +1148,16 @@
         <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H10" t="s">
         <v>30</v>
@@ -1338,13 +1171,13 @@
         <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H11" t="s">
         <v>30</v>
@@ -1358,25 +1191,25 @@
         <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>169</v>
+        <v>120</v>
       </c>
       <c r="G12" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="H12" t="s">
-        <v>149</v>
+        <v>106</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>170</v>
+        <v>121</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>171</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -1387,25 +1220,25 @@
         <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>134</v>
+        <v>91</v>
       </c>
       <c r="E13">
         <v>2023</v>
       </c>
       <c r="F13" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H13" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H13" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="J13" s="1" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -1416,16 +1249,16 @@
         <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H14" t="s">
         <v>30</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>143</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -1436,19 +1269,19 @@
         <v>27</v>
       </c>
       <c r="C15" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="H15" t="s">
         <v>30</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>144</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -1459,25 +1292,25 @@
         <v>25</v>
       </c>
       <c r="C16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" t="s">
+        <v>92</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D16" t="s">
-        <v>135</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="G16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s">
         <v>30</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>145</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
@@ -1488,19 +1321,19 @@
         <v>25</v>
       </c>
       <c r="C17" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" t="s">
+        <v>93</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D17" t="s">
-        <v>136</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="H17" t="s">
         <v>30</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>138</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -1511,10 +1344,10 @@
         <v>25</v>
       </c>
       <c r="C18" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="H18" t="s">
         <v>30</v>
@@ -1528,19 +1361,19 @@
         <v>25</v>
       </c>
       <c r="C19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D19" t="s">
-        <v>137</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="H19" t="s">
         <v>30</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>141</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -1551,10 +1384,10 @@
         <v>25</v>
       </c>
       <c r="C20" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="H20" t="s">
         <v>30</v>
@@ -1568,13 +1401,13 @@
         <v>26</v>
       </c>
       <c r="C21" t="s">
+        <v>76</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="G21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H21" t="s">
         <v>30</v>
@@ -1588,13 +1421,13 @@
         <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>168</v>
+        <v>119</v>
       </c>
       <c r="G22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H22" t="s">
         <v>30</v>
@@ -1602,19 +1435,19 @@
     </row>
     <row r="23" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B23" t="s">
         <v>26</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="3">
+        <v>46026</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="G23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H23" t="s">
         <v>31</v>
@@ -1622,7 +1455,7 @@
     </row>
     <row r="24" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>204</v>
+        <v>133</v>
       </c>
       <c r="B24" t="s">
         <v>26</v>
@@ -1631,10 +1464,10 @@
         <v>33</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="G24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H24" t="s">
         <v>31</v>
@@ -1642,7 +1475,7 @@
     </row>
     <row r="25" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>205</v>
+        <v>134</v>
       </c>
       <c r="B25" t="s">
         <v>26</v>
@@ -1651,10 +1484,10 @@
         <v>33</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>211</v>
+        <v>137</v>
       </c>
       <c r="G25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H25" t="s">
         <v>31</v>
@@ -1662,7 +1495,7 @@
     </row>
     <row r="26" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>206</v>
+        <v>135</v>
       </c>
       <c r="B26" t="s">
         <v>26</v>
@@ -1671,10 +1504,10 @@
         <v>33</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>213</v>
+        <v>138</v>
       </c>
       <c r="G26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H26" t="s">
         <v>31</v>
@@ -1682,7 +1515,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>207</v>
+        <v>140</v>
       </c>
       <c r="B27" t="s">
         <v>26</v>
@@ -1691,10 +1524,10 @@
         <v>33</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>214</v>
+        <v>139</v>
       </c>
       <c r="G27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H27" t="s">
         <v>31</v>
@@ -1714,7 +1547,7 @@
         <v>34</v>
       </c>
       <c r="G28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H28" t="s">
         <v>31</v>
@@ -1722,50 +1555,50 @@
     </row>
     <row r="29" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>208</v>
+        <v>141</v>
       </c>
       <c r="B29" t="s">
         <v>25</v>
       </c>
       <c r="C29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="G29" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H29" t="s">
         <v>31</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>142</v>
+      </c>
+      <c r="B30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" t="s">
+        <v>33</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G30" t="s">
         <v>86</v>
       </c>
-      <c r="B30" t="s">
-        <v>26</v>
-      </c>
-      <c r="C30" t="s">
-        <v>33</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G30" t="s">
-        <v>128</v>
-      </c>
       <c r="H30" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>87</v>
+        <v>143</v>
       </c>
       <c r="B31" t="s">
         <v>26</v>
@@ -1774,18 +1607,18 @@
         <v>33</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>107</v>
+        <v>150</v>
       </c>
       <c r="G31" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="H31" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>88</v>
+        <v>144</v>
       </c>
       <c r="B32" t="s">
         <v>26</v>
@@ -1794,10 +1627,10 @@
         <v>33</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>108</v>
+        <v>151</v>
       </c>
       <c r="G32" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="H32" t="s">
         <v>31</v>
@@ -1805,7 +1638,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
       <c r="B33" t="s">
         <v>26</v>
@@ -1814,10 +1647,10 @@
         <v>33</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>109</v>
+        <v>152</v>
       </c>
       <c r="G33" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="H33" t="s">
         <v>31</v>
@@ -1825,7 +1658,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="B34" t="s">
         <v>26</v>
@@ -1834,18 +1667,18 @@
         <v>33</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="G34" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="H34" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>91</v>
+        <v>147</v>
       </c>
       <c r="B35" t="s">
         <v>26</v>
@@ -1854,18 +1687,18 @@
         <v>33</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>111</v>
+        <v>156</v>
       </c>
       <c r="G35" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="H35" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>126</v>
+        <v>85</v>
       </c>
       <c r="B36" t="s">
         <v>26</v>
@@ -1874,10 +1707,10 @@
         <v>33</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="G36" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="H36" t="s">
         <v>31</v>
@@ -1885,7 +1718,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="B37" t="s">
         <v>26</v>
@@ -1894,10 +1727,10 @@
         <v>33</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G37" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="H37" t="s">
         <v>31</v>
@@ -1905,7 +1738,7 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="B38" t="s">
         <v>26</v>
@@ -1914,10 +1747,10 @@
         <v>33</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G38" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="H38" t="s">
         <v>31</v>
@@ -1925,7 +1758,7 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="B39" t="s">
         <v>26</v>
@@ -1934,10 +1767,10 @@
         <v>33</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G39" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="H39" t="s">
         <v>31</v>
@@ -1945,7 +1778,7 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="B40" t="s">
         <v>26</v>
@@ -1954,10 +1787,10 @@
         <v>33</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G40" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="H40" t="s">
         <v>31</v>
@@ -1965,7 +1798,7 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="B41" t="s">
         <v>26</v>
@@ -1974,30 +1807,30 @@
         <v>33</v>
       </c>
       <c r="F41" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G41" t="s">
+        <v>86</v>
+      </c>
+      <c r="H41" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>115</v>
+      </c>
+      <c r="B42" t="s">
+        <v>26</v>
+      </c>
+      <c r="C42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G41" t="s">
-        <v>128</v>
-      </c>
-      <c r="H41" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>97</v>
-      </c>
-      <c r="B42" t="s">
-        <v>26</v>
-      </c>
-      <c r="C42" t="s">
-        <v>33</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="G42" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="H42" t="s">
         <v>31</v>
@@ -2005,7 +1838,7 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="B43" t="s">
         <v>26</v>
@@ -2014,18 +1847,15 @@
         <v>33</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="G43" t="s">
         <v>128</v>
       </c>
       <c r="H43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="B44" t="s">
         <v>26</v>
@@ -2034,18 +1864,15 @@
         <v>33</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="G44" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="B45" t="s">
         <v>26</v>
@@ -2054,18 +1881,15 @@
         <v>33</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G45" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H45" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>209</v>
+        <v>126</v>
       </c>
       <c r="B46" t="s">
         <v>26</v>
@@ -2074,18 +1898,18 @@
         <v>33</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>212</v>
+        <v>131</v>
       </c>
       <c r="G46" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="H46" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="B47" t="s">
         <v>26</v>
@@ -2094,10 +1918,10 @@
         <v>33</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="G47" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="H47" t="s">
         <v>31</v>
@@ -2105,27 +1929,21 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="B48" t="s">
-        <v>26</v>
+        <v>159</v>
       </c>
       <c r="C48" t="s">
-        <v>33</v>
+        <v>160</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="G48" t="s">
-        <v>128</v>
-      </c>
-      <c r="H48" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>103</v>
+        <v>149</v>
       </c>
       <c r="B49" t="s">
         <v>26</v>
@@ -2134,416 +1952,20 @@
         <v>33</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="G49" t="s">
-        <v>128</v>
-      </c>
-      <c r="H49" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>104</v>
-      </c>
-      <c r="B50" t="s">
-        <v>26</v>
-      </c>
-      <c r="C50" t="s">
-        <v>33</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="G50" t="s">
-        <v>128</v>
-      </c>
-      <c r="H50" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>105</v>
-      </c>
-      <c r="B51" t="s">
-        <v>26</v>
-      </c>
-      <c r="C51" t="s">
-        <v>33</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="G51" t="s">
-        <v>128</v>
-      </c>
-      <c r="H51" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>150</v>
-      </c>
-      <c r="B52" t="s">
-        <v>26</v>
-      </c>
-      <c r="C52" t="s">
-        <v>33</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="G52" t="s">
-        <v>128</v>
-      </c>
-      <c r="H52" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>152</v>
-      </c>
-      <c r="B53" t="s">
-        <v>26</v>
-      </c>
-      <c r="C53" t="s">
-        <v>33</v>
-      </c>
-      <c r="E53">
-        <v>2023</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G53" t="s">
-        <v>128</v>
-      </c>
-      <c r="H53" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>154</v>
-      </c>
-      <c r="B54" t="s">
-        <v>26</v>
-      </c>
-      <c r="C54" t="s">
-        <v>33</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="G54" t="s">
-        <v>128</v>
-      </c>
-      <c r="H54" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>162</v>
-      </c>
-      <c r="B55" t="s">
-        <v>26</v>
-      </c>
-      <c r="C55" t="s">
-        <v>33</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="G55" t="s">
-        <v>128</v>
-      </c>
-      <c r="H55" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>156</v>
-      </c>
-      <c r="B56" t="s">
-        <v>26</v>
-      </c>
-      <c r="C56" t="s">
-        <v>165</v>
-      </c>
-      <c r="E56">
-        <v>2023</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="G56" t="s">
-        <v>128</v>
-      </c>
-      <c r="H56" t="s">
-        <v>31</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>159</v>
-      </c>
-      <c r="B57" t="s">
-        <v>26</v>
-      </c>
-      <c r="C57" t="s">
-        <v>58</v>
-      </c>
-      <c r="E57">
-        <v>2016</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="G57" t="s">
-        <v>128</v>
-      </c>
-      <c r="H57" t="s">
-        <v>31</v>
-      </c>
-      <c r="J57" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>172</v>
-      </c>
-      <c r="B58" t="s">
-        <v>181</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="E58" t="s">
-        <v>182</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="H58" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>173</v>
-      </c>
-      <c r="B59" t="s">
-        <v>181</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E59" t="s">
-        <v>182</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="H59" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>174</v>
-      </c>
-      <c r="B60" t="s">
-        <v>181</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E60" t="s">
-        <v>182</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="H60" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>175</v>
-      </c>
-      <c r="B61" t="s">
-        <v>181</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E61" t="s">
-        <v>182</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="H61" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>176</v>
-      </c>
-      <c r="B62" t="s">
-        <v>181</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="E62" t="s">
-        <v>182</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="H62" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>177</v>
-      </c>
-      <c r="B63" t="s">
-        <v>181</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="E63" t="s">
-        <v>182</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="H63" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>178</v>
-      </c>
-      <c r="B64" t="s">
-        <v>181</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="E64" t="s">
-        <v>195</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="G64" t="s">
-        <v>83</v>
-      </c>
-      <c r="H64" t="s">
-        <v>30</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>179</v>
-      </c>
-      <c r="B65" t="s">
-        <v>181</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E65" t="s">
-        <v>195</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G65" t="s">
-        <v>128</v>
-      </c>
-      <c r="H65" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>163</v>
-      </c>
-      <c r="B66" t="s">
-        <v>26</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="E66" t="s">
-        <v>77</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="G66" t="s">
-        <v>83</v>
-      </c>
-      <c r="H66" t="s">
-        <v>31</v>
-      </c>
-      <c r="I66" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>180</v>
-      </c>
-      <c r="B67" t="s">
-        <v>181</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="E67" t="s">
-        <v>77</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="G67" t="s">
-        <v>128</v>
-      </c>
-      <c r="H67" t="s">
-        <v>31</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="H58:H65 G68:G1048576 H46 G1:G66">
+  <conditionalFormatting sqref="G48:G1048576 H43:H46 G1:G46">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"Outcome"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H58:H65 H46 G1:G1048576">
+  <conditionalFormatting sqref="H43:H46 G1:G1048576">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Covariate"</formula>
     </cfRule>
@@ -2551,4 +1973,13 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50E74FFD-BDC3-480B-B871-F6F13D9BA7E1}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data_plan_capstone.xlsx
+++ b/data_plan_capstone.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabri\Documents\research_capstone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1A31C6-49DE-46A5-9AD4-D3817D18D1C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46D507D1-D353-42A2-BF71-1EC74E0F5B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{84021EAC-F933-478D-95E5-945724B0C9EB}"/>
   </bookViews>
